--- a/outputs/evaluation/requirement/design/v2/gemini-3-5-flash-lite/CF_M01/third/CF_M01_req_eval.xlsx
+++ b/outputs/evaluation/requirement/design/v2/gemini-3-5-flash-lite/CF_M01/third/CF_M01_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.9667</v>
       </c>
       <c r="D13" t="n">
+        <v>0.9831</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9026999999999999</v>
       </c>
     </row>
@@ -755,14 +763,11 @@
           <t>L’estat de la connexió solament pot ser connectat o no connectat.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>R_03</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -776,14 +781,11 @@
           <t>Connections can only have two states: connected or not connected.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>CF_M01_R12</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -814,14 +816,11 @@
           <t>Els usuaris sense permís no poden accedir a les dades de les quals no tenen permís.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>R_26</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -835,14 +834,11 @@
           <t>Unauthorized users cannot access data they do not own.</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>CF_M01_R023</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -873,14 +869,11 @@
           <t>El sistema escala de manera automàtica a la vegada que van augmentant les dades.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>R_24</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -894,14 +887,11 @@
           <t>The system scales automatically as they go increasing the data.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>CF_M01_R24</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -932,14 +922,11 @@
           <t>Totes les accions han d'estar relacionades amb una entitat de la plataforma.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -953,14 +940,11 @@
           <t>All actions must be related to an entity the platform.</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>CF_M01_R015</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -991,14 +975,11 @@
           <t>Les connexions solament podran tenir dos estats: connectat o no connectat.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1012,14 +993,11 @@
           <t>The connection status can only be connected or not connected.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>CF_M01_R03</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1050,10 +1028,6 @@
           <t>Que el sistema guardi les connexions dels players</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1067,10 +1041,6 @@
           <t>System saves player connections</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1106,9 +1076,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1132,8 +1099,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1164,14 +1129,11 @@
           <t>La plataforma escala de forma dinàmica amb els canvis de connexions simultànies.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>R_22</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1185,14 +1147,11 @@
           <t>The platform scales dynamically with changes in connections simultaneous.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>CF_M01_R22</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1223,14 +1182,11 @@
           <t>El sistema respon a qualsevol acció de l’usuari en menys de 5 segons.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>R_18</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1244,14 +1200,11 @@
           <t>The system responds to any user action in less than 5 seconds.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>CF_M01_R018</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1282,14 +1235,11 @@
           <t>S’ha de poder veure tots els detalls del playlog.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>R_09</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1303,14 +1253,11 @@
           <t>You must be able to see all the details of the playlog.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>CF_M01_R09</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1341,10 +1288,6 @@
           <t>Poder llistar les diferents connexions dels players del sistema</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1358,10 +1301,6 @@
           <t>Be able to list the different player connections in the system</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1397,9 +1336,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1423,8 +1359,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1455,14 +1389,11 @@
           <t>Cada acció té una data, client, usuari i player assignat.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>R_06</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1476,14 +1407,11 @@
           <t>Each action has an assigned date, client and player.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>CF_M01_R06</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1514,14 +1442,11 @@
           <t>Els usuaris solament poden observar les dades confidencials del seu usuari i de ningú més.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>R_28</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1535,14 +1460,11 @@
           <t>Users can only view their confidential data user and no one else.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CF_M01_R025</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1573,10 +1495,6 @@
           <t>Que el sistema guardi les accions realitzades sobre la plataforma</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1590,10 +1508,6 @@
           <t>System saves the actions carried out on the platform</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1629,9 +1543,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1655,8 +1566,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1687,10 +1596,6 @@
           <t>Poder llistar les diferents accions que es realitzen sobre les diferents entitats de la plataforma</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1705,10 +1610,6 @@
 platform entities</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1744,9 +1645,6 @@
           <t>C_06</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1771,8 +1669,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1803,14 +1699,11 @@
           <t>Les accions que podrà veure l’usuari dependrà dels permisos que té.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1824,14 +1717,11 @@
           <t>The actions that the user will be able to see will depend on the permissions it has</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>CF_M01_R015</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1862,14 +1752,11 @@
           <t>Qualsevol usuari ha de poder accedir a la plataforma durant qualsevol moment del dia. Excepte en les actualitzacions programades.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1883,14 +1770,11 @@
           <t>Any user must be able to access the platform during any time time of day. Except for scheduled updates.</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>CF_M01_R20</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1921,14 +1805,11 @@
           <t>Cada connexió té una data, client i player assignat.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>R_03</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1942,14 +1823,11 @@
           <t>Each connection has an assigned date, client, player.</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>CF_M01_R03</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1985,9 +1863,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2012,8 +1887,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2044,14 +1917,11 @@
           <t>Totes les accions són realitzades sobre una entitat de la plataforma.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>R_06</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2065,14 +1935,11 @@
           <t>All actions are performed on an entity of the platform.</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>CF_M01_R06</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2103,10 +1970,6 @@
           <t>Que el sistema guardi els playlogs dels players</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2120,10 +1983,6 @@
           <t>System saves the players' playlogs</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2154,10 +2013,6 @@
           <t>Poder llistar els diferents playlogs del sistema</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2171,10 +2026,6 @@
           <t>Be able to list the different playlogs of the system</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2205,14 +2056,11 @@
           <t>Les connexions que podrà veure l’usuari dependrà dels permisos que té.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2226,14 +2074,11 @@
           <t>The connections that the user will be able to see will depend on the permissions it has.</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>CF_M01_R12</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2269,9 +2114,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2295,8 +2137,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2327,14 +2167,11 @@
           <t>Els playlogs que podrà veure l’usuari dependrà dels permisos que té.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>R_09</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2348,14 +2185,11 @@
           <t>The playlogs that the user will be able to see will depend on the permissions it has</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>CF_M01_R09</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2386,14 +2220,11 @@
           <t>Cada playlog té una data, client i player assignat.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2407,14 +2238,11 @@
           <t>Each playlog has an assigned date, client, player.</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>CF_M01_R01</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
